--- a/datasets/test/イチゴ/59期収量（全体）.xlsx
+++ b/datasets/test/イチゴ/59期収量（全体）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\B000005_営業本部　ハウス備品事業本部\障がい者農園事業部\004_はーとふる農園　愛川\農業指導員\砂栽培研究\イチゴ栽培\59期\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\matsuoka\heartful-agri-lab\datasets\test\イチゴ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467FA43E-BB5A-43BD-9DDD-F2BE9F3C9C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D5E72E-5BFF-41EB-87C3-FEEEFFA248C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="46">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -234,6 +234,10 @@
   </si>
   <si>
     <t>合計 / やよいひめ</t>
+  </si>
+  <si>
+    <t>ここまで</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1730,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.08203125" bestFit="1" customWidth="1"/>
@@ -3318,7 +3322,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>46086</v>
       </c>
@@ -3330,6 +3334,9 @@
       </c>
       <c r="D113">
         <v>1140</v>
+      </c>
+      <c r="I113" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
